--- a/src/data/excel/behemoth_skills.xlsx
+++ b/src/data/excel/behemoth_skills.xlsx
@@ -3,8 +3,12 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="MK III Skills" sheetId="1" r:id="rId1"/>
-    <sheet name="MK IV Skills" sheetId="2" r:id="rId2"/>
+    <sheet name="MK 0 Skills" sheetId="1" r:id="rId1"/>
+    <sheet name="MK III Skills" sheetId="2" r:id="rId2"/>
+    <sheet name="MK IV Skills" sheetId="3" r:id="rId3"/>
+    <sheet name="MK I Skills" sheetId="4" r:id="rId4"/>
+    <sheet name="MK II Skills" sheetId="5" r:id="rId5"/>
+    <sheet name="MK V Skills" sheetId="6" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
@@ -398,6 +402,5984 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E351"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tree</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Skill</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Level</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Benefit</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Neuronal Medium</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="str">
+        <v>+1 minute</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3" t="str">
+        <v>+2 minutes</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4" t="str">
+        <v>+3 minutes</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5" t="str">
+        <v>+4 minutes</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6" t="str">
+        <v>+5 minutes</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+      <c r="D7" t="str">
+        <v>+6 minutes</v>
+      </c>
+      <c r="E7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="C8">
+        <v>7</v>
+      </c>
+      <c r="D8" t="str">
+        <v>+7 minutes</v>
+      </c>
+      <c r="E8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="C9">
+        <v>8</v>
+      </c>
+      <c r="D9" t="str">
+        <v>+8 minutes</v>
+      </c>
+      <c r="E9">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="C10">
+        <v>9</v>
+      </c>
+      <c r="D10" t="str">
+        <v>+9 minutes</v>
+      </c>
+      <c r="E10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="C11">
+        <v>10</v>
+      </c>
+      <c r="D11" t="str">
+        <v>+10 minutes</v>
+      </c>
+      <c r="E11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Efficient Construction</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12" t="str">
+        <v>+0.5%</v>
+      </c>
+      <c r="E12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Efficient Construction</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+      <c r="D13" t="str">
+        <v>+1%</v>
+      </c>
+      <c r="E13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Efficient Construction</v>
+      </c>
+      <c r="C14">
+        <v>3</v>
+      </c>
+      <c r="D14" t="str">
+        <v>1.5%</v>
+      </c>
+      <c r="E14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Efficient Construction</v>
+      </c>
+      <c r="C15">
+        <v>4</v>
+      </c>
+      <c r="D15" t="str">
+        <v>+2%</v>
+      </c>
+      <c r="E15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Efficient Construction</v>
+      </c>
+      <c r="C16">
+        <v>5</v>
+      </c>
+      <c r="D16" t="str">
+        <v>+2.5%</v>
+      </c>
+      <c r="E16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Efficient Construction</v>
+      </c>
+      <c r="C17">
+        <v>6</v>
+      </c>
+      <c r="D17" t="str">
+        <v>+3%</v>
+      </c>
+      <c r="E17">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Efficient Construction</v>
+      </c>
+      <c r="C18">
+        <v>7</v>
+      </c>
+      <c r="D18" t="str">
+        <v>+3.5%</v>
+      </c>
+      <c r="E18">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Efficient Construction</v>
+      </c>
+      <c r="C19">
+        <v>8</v>
+      </c>
+      <c r="D19" t="str">
+        <v>+4%</v>
+      </c>
+      <c r="E19">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Efficient Construction</v>
+      </c>
+      <c r="C20">
+        <v>9</v>
+      </c>
+      <c r="D20" t="str">
+        <v>+4.5%</v>
+      </c>
+      <c r="E20">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Efficient Construction</v>
+      </c>
+      <c r="C21">
+        <v>10</v>
+      </c>
+      <c r="D21" t="str">
+        <v>+5%</v>
+      </c>
+      <c r="E21">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Research Progress</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22" t="str">
+        <v>+0.3%</v>
+      </c>
+      <c r="E22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Research Progress</v>
+      </c>
+      <c r="C23">
+        <v>2</v>
+      </c>
+      <c r="D23" t="str">
+        <v>+0.6%</v>
+      </c>
+      <c r="E23">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Research Progress</v>
+      </c>
+      <c r="C24">
+        <v>3</v>
+      </c>
+      <c r="D24" t="str">
+        <v>+0.9%</v>
+      </c>
+      <c r="E24">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Research Progress</v>
+      </c>
+      <c r="C25">
+        <v>4</v>
+      </c>
+      <c r="D25" t="str">
+        <v>+1.2%</v>
+      </c>
+      <c r="E25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Research Progress</v>
+      </c>
+      <c r="C26">
+        <v>5</v>
+      </c>
+      <c r="D26" t="str">
+        <v>+1.5%</v>
+      </c>
+      <c r="E26">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Research Progress</v>
+      </c>
+      <c r="C27">
+        <v>6</v>
+      </c>
+      <c r="D27" t="str">
+        <v>+1.8%</v>
+      </c>
+      <c r="E27">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Research Progress</v>
+      </c>
+      <c r="C28">
+        <v>7</v>
+      </c>
+      <c r="D28" t="str">
+        <v>+2.1%</v>
+      </c>
+      <c r="E28">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Research Progress</v>
+      </c>
+      <c r="C29">
+        <v>8</v>
+      </c>
+      <c r="D29" t="str">
+        <v>+2.4%</v>
+      </c>
+      <c r="E29">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Research Progress</v>
+      </c>
+      <c r="C30">
+        <v>9</v>
+      </c>
+      <c r="D30" t="str">
+        <v>+2.7%</v>
+      </c>
+      <c r="E30">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Research Progress</v>
+      </c>
+      <c r="C31">
+        <v>10</v>
+      </c>
+      <c r="D31" t="str">
+        <v>+3%</v>
+      </c>
+      <c r="E31">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Building Materials</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32" t="str">
+        <v>-0.2%</v>
+      </c>
+      <c r="E32">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Building Materials</v>
+      </c>
+      <c r="C33">
+        <v>2</v>
+      </c>
+      <c r="D33" t="str">
+        <v>-0.4%</v>
+      </c>
+      <c r="E33">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Building Materials</v>
+      </c>
+      <c r="C34">
+        <v>3</v>
+      </c>
+      <c r="D34" t="str">
+        <v>-0.6%</v>
+      </c>
+      <c r="E34">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Building Materials</v>
+      </c>
+      <c r="C35">
+        <v>4</v>
+      </c>
+      <c r="D35" t="str">
+        <v>-0.8%</v>
+      </c>
+      <c r="E35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Building Materials</v>
+      </c>
+      <c r="C36">
+        <v>5</v>
+      </c>
+      <c r="D36" t="str">
+        <v>-1%</v>
+      </c>
+      <c r="E36">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Building Materials</v>
+      </c>
+      <c r="C37">
+        <v>6</v>
+      </c>
+      <c r="D37" t="str">
+        <v>-1.2%</v>
+      </c>
+      <c r="E37">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Building Materials</v>
+      </c>
+      <c r="C38">
+        <v>7</v>
+      </c>
+      <c r="D38" t="str">
+        <v>-1.4%</v>
+      </c>
+      <c r="E38">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Building Materials</v>
+      </c>
+      <c r="C39">
+        <v>8</v>
+      </c>
+      <c r="D39" t="str">
+        <v>-1.6%</v>
+      </c>
+      <c r="E39">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Building Materials</v>
+      </c>
+      <c r="C40">
+        <v>9</v>
+      </c>
+      <c r="D40" t="str">
+        <v>-1.8%</v>
+      </c>
+      <c r="E40">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Building Materials</v>
+      </c>
+      <c r="C41">
+        <v>10</v>
+      </c>
+      <c r="D41" t="str">
+        <v>-2%</v>
+      </c>
+      <c r="E41">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Training Expansion</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+      <c r="D42" t="str">
+        <v>+2</v>
+      </c>
+      <c r="E42">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Training Expansion</v>
+      </c>
+      <c r="C43">
+        <v>2</v>
+      </c>
+      <c r="D43" t="str">
+        <v>+4</v>
+      </c>
+      <c r="E43">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Training Expansion</v>
+      </c>
+      <c r="C44">
+        <v>3</v>
+      </c>
+      <c r="D44" t="str">
+        <v>+6</v>
+      </c>
+      <c r="E44">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Training Expansion</v>
+      </c>
+      <c r="C45">
+        <v>4</v>
+      </c>
+      <c r="D45" t="str">
+        <v>+8</v>
+      </c>
+      <c r="E45">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Training Expansion</v>
+      </c>
+      <c r="C46">
+        <v>5</v>
+      </c>
+      <c r="D46" t="str">
+        <v>+10</v>
+      </c>
+      <c r="E46">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Training Expansion</v>
+      </c>
+      <c r="C47">
+        <v>6</v>
+      </c>
+      <c r="D47" t="str">
+        <v>+12</v>
+      </c>
+      <c r="E47">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Training Expansion</v>
+      </c>
+      <c r="C48">
+        <v>7</v>
+      </c>
+      <c r="D48" t="str">
+        <v>+14</v>
+      </c>
+      <c r="E48">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Training Expansion</v>
+      </c>
+      <c r="C49">
+        <v>8</v>
+      </c>
+      <c r="D49" t="str">
+        <v>+16</v>
+      </c>
+      <c r="E49">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Training Expansion</v>
+      </c>
+      <c r="C50">
+        <v>9</v>
+      </c>
+      <c r="D50" t="str">
+        <v>+18</v>
+      </c>
+      <c r="E50">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Training Expansion</v>
+      </c>
+      <c r="C51">
+        <v>10</v>
+      </c>
+      <c r="D51" t="str">
+        <v>+20</v>
+      </c>
+      <c r="E51">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B52" t="str">
+        <v>Speedy Training</v>
+      </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
+      <c r="D52" t="str">
+        <v>+1%</v>
+      </c>
+      <c r="E52">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B53" t="str">
+        <v>Speedy Training</v>
+      </c>
+      <c r="C53">
+        <v>2</v>
+      </c>
+      <c r="D53" t="str">
+        <v>+2%</v>
+      </c>
+      <c r="E53">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B54" t="str">
+        <v>Speedy Training</v>
+      </c>
+      <c r="C54">
+        <v>3</v>
+      </c>
+      <c r="D54" t="str">
+        <v>+3%</v>
+      </c>
+      <c r="E54">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B55" t="str">
+        <v>Speedy Training</v>
+      </c>
+      <c r="C55">
+        <v>4</v>
+      </c>
+      <c r="D55" t="str">
+        <v>+4%</v>
+      </c>
+      <c r="E55">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B56" t="str">
+        <v>Speedy Training</v>
+      </c>
+      <c r="C56">
+        <v>5</v>
+      </c>
+      <c r="D56" t="str">
+        <v>+5%</v>
+      </c>
+      <c r="E56">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B57" t="str">
+        <v>Speedy Training</v>
+      </c>
+      <c r="C57">
+        <v>6</v>
+      </c>
+      <c r="D57" t="str">
+        <v>+6%</v>
+      </c>
+      <c r="E57">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B58" t="str">
+        <v>Speedy Training</v>
+      </c>
+      <c r="C58">
+        <v>7</v>
+      </c>
+      <c r="D58" t="str">
+        <v>+7%</v>
+      </c>
+      <c r="E58">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B59" t="str">
+        <v>Speedy Training</v>
+      </c>
+      <c r="C59">
+        <v>8</v>
+      </c>
+      <c r="D59" t="str">
+        <v>+8%</v>
+      </c>
+      <c r="E59">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B60" t="str">
+        <v>Speedy Training</v>
+      </c>
+      <c r="C60">
+        <v>9</v>
+      </c>
+      <c r="D60" t="str">
+        <v>+9%</v>
+      </c>
+      <c r="E60">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B61" t="str">
+        <v>Speedy Training</v>
+      </c>
+      <c r="C61">
+        <v>10</v>
+      </c>
+      <c r="D61" t="str">
+        <v>+10%</v>
+      </c>
+      <c r="E61">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B62" t="str">
+        <v>Training Resorces</v>
+      </c>
+      <c r="C62">
+        <v>1</v>
+      </c>
+      <c r="D62" t="str">
+        <v>-0.1%</v>
+      </c>
+      <c r="E62">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B63" t="str">
+        <v>Training Resorces</v>
+      </c>
+      <c r="C63">
+        <v>2</v>
+      </c>
+      <c r="D63" t="str">
+        <v>-0.2%</v>
+      </c>
+      <c r="E63">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B64" t="str">
+        <v>Training Resorces</v>
+      </c>
+      <c r="C64">
+        <v>3</v>
+      </c>
+      <c r="D64" t="str">
+        <v>-0.3%</v>
+      </c>
+      <c r="E64">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B65" t="str">
+        <v>Training Resorces</v>
+      </c>
+      <c r="C65">
+        <v>4</v>
+      </c>
+      <c r="D65" t="str">
+        <v>-0.4%</v>
+      </c>
+      <c r="E65">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B66" t="str">
+        <v>Training Resorces</v>
+      </c>
+      <c r="C66">
+        <v>5</v>
+      </c>
+      <c r="D66" t="str">
+        <v>-0.5%</v>
+      </c>
+      <c r="E66">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B67" t="str">
+        <v>Training Resorces</v>
+      </c>
+      <c r="C67">
+        <v>6</v>
+      </c>
+      <c r="D67" t="str">
+        <v>-0.6%</v>
+      </c>
+      <c r="E67">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B68" t="str">
+        <v>Training Resorces</v>
+      </c>
+      <c r="C68">
+        <v>7</v>
+      </c>
+      <c r="D68" t="str">
+        <v>-0.7%</v>
+      </c>
+      <c r="E68">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B69" t="str">
+        <v>Training Resorces</v>
+      </c>
+      <c r="C69">
+        <v>8</v>
+      </c>
+      <c r="D69" t="str">
+        <v>-0.8%</v>
+      </c>
+      <c r="E69">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B70" t="str">
+        <v>Training Resorces</v>
+      </c>
+      <c r="C70">
+        <v>9</v>
+      </c>
+      <c r="D70" t="str">
+        <v>-0.9%</v>
+      </c>
+      <c r="E70">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B71" t="str">
+        <v>Training Resorces</v>
+      </c>
+      <c r="C71">
+        <v>10</v>
+      </c>
+      <c r="D71" t="str">
+        <v>-10%</v>
+      </c>
+      <c r="E71">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B72" t="str">
+        <v>Food Gathering</v>
+      </c>
+      <c r="C72">
+        <v>1</v>
+      </c>
+      <c r="D72" t="str">
+        <v>+2%</v>
+      </c>
+      <c r="E72">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B73" t="str">
+        <v>Food Gathering</v>
+      </c>
+      <c r="C73">
+        <v>2</v>
+      </c>
+      <c r="D73" t="str">
+        <v>+4%</v>
+      </c>
+      <c r="E73">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B74" t="str">
+        <v>Food Gathering</v>
+      </c>
+      <c r="C74">
+        <v>3</v>
+      </c>
+      <c r="D74" t="str">
+        <v>+6%</v>
+      </c>
+      <c r="E74">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B75" t="str">
+        <v>Food Gathering</v>
+      </c>
+      <c r="C75">
+        <v>4</v>
+      </c>
+      <c r="D75" t="str">
+        <v>+8%</v>
+      </c>
+      <c r="E75">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B76" t="str">
+        <v>Food Gathering</v>
+      </c>
+      <c r="C76">
+        <v>5</v>
+      </c>
+      <c r="D76" t="str">
+        <v>+10%</v>
+      </c>
+      <c r="E76">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B77" t="str">
+        <v>Food Gathering</v>
+      </c>
+      <c r="C77">
+        <v>6</v>
+      </c>
+      <c r="D77" t="str">
+        <v>+12%</v>
+      </c>
+      <c r="E77">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B78" t="str">
+        <v>Food Gathering</v>
+      </c>
+      <c r="C78">
+        <v>7</v>
+      </c>
+      <c r="D78" t="str">
+        <v>+14%</v>
+      </c>
+      <c r="E78">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B79" t="str">
+        <v>Food Gathering</v>
+      </c>
+      <c r="C79">
+        <v>8</v>
+      </c>
+      <c r="D79" t="str">
+        <v>+16%</v>
+      </c>
+      <c r="E79">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B80" t="str">
+        <v>Food Gathering</v>
+      </c>
+      <c r="C80">
+        <v>9</v>
+      </c>
+      <c r="D80" t="str">
+        <v>+18%</v>
+      </c>
+      <c r="E80">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B81" t="str">
+        <v>Food Gathering</v>
+      </c>
+      <c r="C81">
+        <v>10</v>
+      </c>
+      <c r="D81" t="str">
+        <v>+20%</v>
+      </c>
+      <c r="E81">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B82" t="str">
+        <v>Wood Gathering</v>
+      </c>
+      <c r="C82">
+        <v>1</v>
+      </c>
+      <c r="D82" t="str">
+        <v>+2%</v>
+      </c>
+      <c r="E82">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B83" t="str">
+        <v>Wood Gathering</v>
+      </c>
+      <c r="C83">
+        <v>2</v>
+      </c>
+      <c r="D83" t="str">
+        <v>+4%</v>
+      </c>
+      <c r="E83">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B84" t="str">
+        <v>Wood Gathering</v>
+      </c>
+      <c r="C84">
+        <v>3</v>
+      </c>
+      <c r="D84" t="str">
+        <v>+6%</v>
+      </c>
+      <c r="E84">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B85" t="str">
+        <v>Wood Gathering</v>
+      </c>
+      <c r="C85">
+        <v>4</v>
+      </c>
+      <c r="D85" t="str">
+        <v>+8%</v>
+      </c>
+      <c r="E85">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B86" t="str">
+        <v>Wood Gathering</v>
+      </c>
+      <c r="C86">
+        <v>5</v>
+      </c>
+      <c r="D86" t="str">
+        <v>+10%</v>
+      </c>
+      <c r="E86">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B87" t="str">
+        <v>Wood Gathering</v>
+      </c>
+      <c r="C87">
+        <v>6</v>
+      </c>
+      <c r="D87" t="str">
+        <v>+12%</v>
+      </c>
+      <c r="E87">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B88" t="str">
+        <v>Wood Gathering</v>
+      </c>
+      <c r="C88">
+        <v>7</v>
+      </c>
+      <c r="D88" t="str">
+        <v>+14%</v>
+      </c>
+      <c r="E88">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B89" t="str">
+        <v>Wood Gathering</v>
+      </c>
+      <c r="C89">
+        <v>8</v>
+      </c>
+      <c r="D89" t="str">
+        <v>+16%</v>
+      </c>
+      <c r="E89">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B90" t="str">
+        <v>Wood Gathering</v>
+      </c>
+      <c r="C90">
+        <v>9</v>
+      </c>
+      <c r="D90" t="str">
+        <v>+18%</v>
+      </c>
+      <c r="E90">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B91" t="str">
+        <v>Wood Gathering</v>
+      </c>
+      <c r="C91">
+        <v>10</v>
+      </c>
+      <c r="D91" t="str">
+        <v>+20%</v>
+      </c>
+      <c r="E91">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B92" t="str">
+        <v>Metal Gathering</v>
+      </c>
+      <c r="C92">
+        <v>1</v>
+      </c>
+      <c r="D92" t="str">
+        <v>+2%</v>
+      </c>
+      <c r="E92">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B93" t="str">
+        <v>Metal Gathering</v>
+      </c>
+      <c r="C93">
+        <v>2</v>
+      </c>
+      <c r="D93" t="str">
+        <v>+4%</v>
+      </c>
+      <c r="E93">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B94" t="str">
+        <v>Metal Gathering</v>
+      </c>
+      <c r="C94">
+        <v>3</v>
+      </c>
+      <c r="D94" t="str">
+        <v>+6%</v>
+      </c>
+      <c r="E94">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B95" t="str">
+        <v>Metal Gathering</v>
+      </c>
+      <c r="C95">
+        <v>4</v>
+      </c>
+      <c r="D95" t="str">
+        <v>+8%</v>
+      </c>
+      <c r="E95">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B96" t="str">
+        <v>Metal Gathering</v>
+      </c>
+      <c r="C96">
+        <v>5</v>
+      </c>
+      <c r="D96" t="str">
+        <v>+10%</v>
+      </c>
+      <c r="E96">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B97" t="str">
+        <v>Metal Gathering</v>
+      </c>
+      <c r="C97">
+        <v>6</v>
+      </c>
+      <c r="D97" t="str">
+        <v>+12%</v>
+      </c>
+      <c r="E97">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B98" t="str">
+        <v>Metal Gathering</v>
+      </c>
+      <c r="C98">
+        <v>7</v>
+      </c>
+      <c r="D98" t="str">
+        <v>+14%</v>
+      </c>
+      <c r="E98">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B99" t="str">
+        <v>Metal Gathering</v>
+      </c>
+      <c r="C99">
+        <v>8</v>
+      </c>
+      <c r="D99" t="str">
+        <v>+16%</v>
+      </c>
+      <c r="E99">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B100" t="str">
+        <v>Metal Gathering</v>
+      </c>
+      <c r="C100">
+        <v>9</v>
+      </c>
+      <c r="D100" t="str">
+        <v>+18%</v>
+      </c>
+      <c r="E100">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B101" t="str">
+        <v>Metal Gathering</v>
+      </c>
+      <c r="C101">
+        <v>10</v>
+      </c>
+      <c r="D101" t="str">
+        <v>+20%</v>
+      </c>
+      <c r="E101">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B102" t="str">
+        <v>Gas Gathering</v>
+      </c>
+      <c r="C102">
+        <v>1</v>
+      </c>
+      <c r="D102" t="str">
+        <v>+2%</v>
+      </c>
+      <c r="E102">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B103" t="str">
+        <v>Gas Gathering</v>
+      </c>
+      <c r="C103">
+        <v>2</v>
+      </c>
+      <c r="D103" t="str">
+        <v>+4%</v>
+      </c>
+      <c r="E103">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B104" t="str">
+        <v>Gas Gathering</v>
+      </c>
+      <c r="C104">
+        <v>3</v>
+      </c>
+      <c r="D104" t="str">
+        <v>+6%</v>
+      </c>
+      <c r="E104">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B105" t="str">
+        <v>Gas Gathering</v>
+      </c>
+      <c r="C105">
+        <v>4</v>
+      </c>
+      <c r="D105" t="str">
+        <v>+8%</v>
+      </c>
+      <c r="E105">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B106" t="str">
+        <v>Gas Gathering</v>
+      </c>
+      <c r="C106">
+        <v>5</v>
+      </c>
+      <c r="D106" t="str">
+        <v>+10%</v>
+      </c>
+      <c r="E106">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B107" t="str">
+        <v>Gas Gathering</v>
+      </c>
+      <c r="C107">
+        <v>6</v>
+      </c>
+      <c r="D107" t="str">
+        <v>+12%</v>
+      </c>
+      <c r="E107">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B108" t="str">
+        <v>Gas Gathering</v>
+      </c>
+      <c r="C108">
+        <v>7</v>
+      </c>
+      <c r="D108" t="str">
+        <v>+14%</v>
+      </c>
+      <c r="E108">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B109" t="str">
+        <v>Gas Gathering</v>
+      </c>
+      <c r="C109">
+        <v>8</v>
+      </c>
+      <c r="D109" t="str">
+        <v>+16%</v>
+      </c>
+      <c r="E109">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B110" t="str">
+        <v>Gas Gathering</v>
+      </c>
+      <c r="C110">
+        <v>9</v>
+      </c>
+      <c r="D110" t="str">
+        <v>+18%</v>
+      </c>
+      <c r="E110">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>Construction Time</v>
+      </c>
+      <c r="B111" t="str">
+        <v>Gas Gathering</v>
+      </c>
+      <c r="C111">
+        <v>10</v>
+      </c>
+      <c r="D111" t="str">
+        <v>+20%</v>
+      </c>
+      <c r="E111">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B112" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="C112">
+        <v>1</v>
+      </c>
+      <c r="D112" t="str">
+        <v>+1.9%</v>
+      </c>
+      <c r="E112">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B113" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="C113">
+        <v>2</v>
+      </c>
+      <c r="D113" t="str">
+        <v>+3.8%</v>
+      </c>
+      <c r="E113">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B114" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="C114">
+        <v>3</v>
+      </c>
+      <c r="D114" t="str">
+        <v>+5.8%</v>
+      </c>
+      <c r="E114">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B115" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="C115">
+        <v>4</v>
+      </c>
+      <c r="D115" t="str">
+        <v>+7.7%</v>
+      </c>
+      <c r="E115">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B116" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="C116">
+        <v>5</v>
+      </c>
+      <c r="D116" t="str">
+        <v>+9.6%</v>
+      </c>
+      <c r="E116">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B117" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="C117">
+        <v>6</v>
+      </c>
+      <c r="D117" t="str">
+        <v>+11.5%</v>
+      </c>
+      <c r="E117">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B118" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="C118">
+        <v>7</v>
+      </c>
+      <c r="D118" t="str">
+        <v>+13.4%</v>
+      </c>
+      <c r="E118">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B119" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="C119">
+        <v>8</v>
+      </c>
+      <c r="D119" t="str">
+        <v>+15.4%</v>
+      </c>
+      <c r="E119">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B120" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="C120">
+        <v>9</v>
+      </c>
+      <c r="D120" t="str">
+        <v>+17.3%</v>
+      </c>
+      <c r="E120">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B121" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="C121">
+        <v>10</v>
+      </c>
+      <c r="D121" t="str">
+        <v>+19.2%</v>
+      </c>
+      <c r="E121">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B122" t="str">
+        <v>Rider Defense</v>
+      </c>
+      <c r="C122">
+        <v>1</v>
+      </c>
+      <c r="D122" t="str">
+        <v>+1.9%</v>
+      </c>
+      <c r="E122">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B123" t="str">
+        <v>Rider Defense</v>
+      </c>
+      <c r="C123">
+        <v>2</v>
+      </c>
+      <c r="D123" t="str">
+        <v>+3.8%</v>
+      </c>
+      <c r="E123">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B124" t="str">
+        <v>Rider Defense</v>
+      </c>
+      <c r="C124">
+        <v>3</v>
+      </c>
+      <c r="D124" t="str">
+        <v>+5.8%</v>
+      </c>
+      <c r="E124">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B125" t="str">
+        <v>Rider Defense</v>
+      </c>
+      <c r="C125">
+        <v>4</v>
+      </c>
+      <c r="D125" t="str">
+        <v>+7.7%</v>
+      </c>
+      <c r="E125">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B126" t="str">
+        <v>Rider Defense</v>
+      </c>
+      <c r="C126">
+        <v>5</v>
+      </c>
+      <c r="D126" t="str">
+        <v>+9.6%</v>
+      </c>
+      <c r="E126">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B127" t="str">
+        <v>Rider Defense</v>
+      </c>
+      <c r="C127">
+        <v>6</v>
+      </c>
+      <c r="D127" t="str">
+        <v>+11.5%</v>
+      </c>
+      <c r="E127">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B128" t="str">
+        <v>Rider Defense</v>
+      </c>
+      <c r="C128">
+        <v>7</v>
+      </c>
+      <c r="D128" t="str">
+        <v>+13.4%</v>
+      </c>
+      <c r="E128">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B129" t="str">
+        <v>Rider Defense</v>
+      </c>
+      <c r="C129">
+        <v>8</v>
+      </c>
+      <c r="D129" t="str">
+        <v>+15.4%</v>
+      </c>
+      <c r="E129">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B130" t="str">
+        <v>Rider Defense</v>
+      </c>
+      <c r="C130">
+        <v>9</v>
+      </c>
+      <c r="D130" t="str">
+        <v>+17.3%</v>
+      </c>
+      <c r="E130">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B131" t="str">
+        <v>Rider Defense</v>
+      </c>
+      <c r="C131">
+        <v>10</v>
+      </c>
+      <c r="D131" t="str">
+        <v>+19.2%</v>
+      </c>
+      <c r="E131">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B132" t="str">
+        <v>Infantry Defense</v>
+      </c>
+      <c r="C132">
+        <v>1</v>
+      </c>
+      <c r="D132" t="str">
+        <v>+1.9%</v>
+      </c>
+      <c r="E132">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B133" t="str">
+        <v>Infantry Defense</v>
+      </c>
+      <c r="C133">
+        <v>2</v>
+      </c>
+      <c r="D133" t="str">
+        <v>+3.8%</v>
+      </c>
+      <c r="E133">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B134" t="str">
+        <v>Infantry Defense</v>
+      </c>
+      <c r="C134">
+        <v>3</v>
+      </c>
+      <c r="D134" t="str">
+        <v>+5.8%</v>
+      </c>
+      <c r="E134">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B135" t="str">
+        <v>Infantry Defense</v>
+      </c>
+      <c r="C135">
+        <v>4</v>
+      </c>
+      <c r="D135" t="str">
+        <v>+7.7%</v>
+      </c>
+      <c r="E135">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B136" t="str">
+        <v>Infantry Defense</v>
+      </c>
+      <c r="C136">
+        <v>5</v>
+      </c>
+      <c r="D136" t="str">
+        <v>+9.6%</v>
+      </c>
+      <c r="E136">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B137" t="str">
+        <v>Infantry Defense</v>
+      </c>
+      <c r="C137">
+        <v>6</v>
+      </c>
+      <c r="D137" t="str">
+        <v>+11.5%</v>
+      </c>
+      <c r="E137">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B138" t="str">
+        <v>Infantry Defense</v>
+      </c>
+      <c r="C138">
+        <v>7</v>
+      </c>
+      <c r="D138" t="str">
+        <v>+13.4%</v>
+      </c>
+      <c r="E138">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B139" t="str">
+        <v>Infantry Defense</v>
+      </c>
+      <c r="C139">
+        <v>8</v>
+      </c>
+      <c r="D139" t="str">
+        <v>+15.4%</v>
+      </c>
+      <c r="E139">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B140" t="str">
+        <v>Infantry Defense</v>
+      </c>
+      <c r="C140">
+        <v>9</v>
+      </c>
+      <c r="D140" t="str">
+        <v>+17.3%</v>
+      </c>
+      <c r="E140">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B141" t="str">
+        <v>Infantry Defense</v>
+      </c>
+      <c r="C141">
+        <v>10</v>
+      </c>
+      <c r="D141" t="str">
+        <v>+19.2%</v>
+      </c>
+      <c r="E141">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B142" t="str">
+        <v>Infantry Lethality</v>
+      </c>
+      <c r="C142">
+        <v>1</v>
+      </c>
+      <c r="D142" t="str">
+        <v>+1.4%</v>
+      </c>
+      <c r="E142">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B143" t="str">
+        <v>Infantry Lethality</v>
+      </c>
+      <c r="C143">
+        <v>2</v>
+      </c>
+      <c r="D143" t="str">
+        <v>+2.9%</v>
+      </c>
+      <c r="E143">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B144" t="str">
+        <v>Infantry Lethality</v>
+      </c>
+      <c r="C144">
+        <v>3</v>
+      </c>
+      <c r="D144" t="str">
+        <v>+4.3%</v>
+      </c>
+      <c r="E144">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B145" t="str">
+        <v>Infantry Lethality</v>
+      </c>
+      <c r="C145">
+        <v>4</v>
+      </c>
+      <c r="D145" t="str">
+        <v>+5.8%</v>
+      </c>
+      <c r="E145">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B146" t="str">
+        <v>Infantry Lethality</v>
+      </c>
+      <c r="C146">
+        <v>5</v>
+      </c>
+      <c r="D146" t="str">
+        <v>+7.2%</v>
+      </c>
+      <c r="E146">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B147" t="str">
+        <v>Infantry Lethality</v>
+      </c>
+      <c r="C147">
+        <v>6</v>
+      </c>
+      <c r="D147" t="str">
+        <v>+8.6%</v>
+      </c>
+      <c r="E147">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B148" t="str">
+        <v>Infantry Lethality</v>
+      </c>
+      <c r="C148">
+        <v>7</v>
+      </c>
+      <c r="D148" t="str">
+        <v>+10.1%</v>
+      </c>
+      <c r="E148">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B149" t="str">
+        <v>Infantry Lethality</v>
+      </c>
+      <c r="C149">
+        <v>8</v>
+      </c>
+      <c r="D149" t="str">
+        <v>+11.5%</v>
+      </c>
+      <c r="E149">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B150" t="str">
+        <v>Infantry Lethality</v>
+      </c>
+      <c r="C150">
+        <v>9</v>
+      </c>
+      <c r="D150" t="str">
+        <v>+13%</v>
+      </c>
+      <c r="E150">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B151" t="str">
+        <v>Infantry Lethality</v>
+      </c>
+      <c r="C151">
+        <v>10</v>
+      </c>
+      <c r="D151" t="str">
+        <v>+14.4%</v>
+      </c>
+      <c r="E151">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B152" t="str">
+        <v>Infantry Health</v>
+      </c>
+      <c r="C152">
+        <v>1</v>
+      </c>
+      <c r="D152" t="str">
+        <v>+1.4%</v>
+      </c>
+      <c r="E152">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B153" t="str">
+        <v>Infantry Health</v>
+      </c>
+      <c r="C153">
+        <v>2</v>
+      </c>
+      <c r="D153" t="str">
+        <v>+2.9%</v>
+      </c>
+      <c r="E153">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B154" t="str">
+        <v>Infantry Health</v>
+      </c>
+      <c r="C154">
+        <v>3</v>
+      </c>
+      <c r="D154" t="str">
+        <v>+4.3%</v>
+      </c>
+      <c r="E154">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B155" t="str">
+        <v>Infantry Health</v>
+      </c>
+      <c r="C155">
+        <v>4</v>
+      </c>
+      <c r="D155" t="str">
+        <v>+5.8%</v>
+      </c>
+      <c r="E155">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B156" t="str">
+        <v>Infantry Health</v>
+      </c>
+      <c r="C156">
+        <v>5</v>
+      </c>
+      <c r="D156" t="str">
+        <v>+7.2%</v>
+      </c>
+      <c r="E156">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B157" t="str">
+        <v>Infantry Health</v>
+      </c>
+      <c r="C157">
+        <v>6</v>
+      </c>
+      <c r="D157" t="str">
+        <v>+8.6%</v>
+      </c>
+      <c r="E157">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B158" t="str">
+        <v>Infantry Health</v>
+      </c>
+      <c r="C158">
+        <v>7</v>
+      </c>
+      <c r="D158" t="str">
+        <v>+10.1%</v>
+      </c>
+      <c r="E158">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B159" t="str">
+        <v>Infantry Health</v>
+      </c>
+      <c r="C159">
+        <v>8</v>
+      </c>
+      <c r="D159" t="str">
+        <v>+11.5%</v>
+      </c>
+      <c r="E159">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B160" t="str">
+        <v>Infantry Health</v>
+      </c>
+      <c r="C160">
+        <v>9</v>
+      </c>
+      <c r="D160" t="str">
+        <v>+13%</v>
+      </c>
+      <c r="E160">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B161" t="str">
+        <v>Infantry Health</v>
+      </c>
+      <c r="C161">
+        <v>10</v>
+      </c>
+      <c r="D161" t="str">
+        <v>+14.4%</v>
+      </c>
+      <c r="E161">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B162" t="str">
+        <v>Hunter Defense</v>
+      </c>
+      <c r="C162">
+        <v>1</v>
+      </c>
+      <c r="D162" t="str">
+        <v>+1.9%</v>
+      </c>
+      <c r="E162">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B163" t="str">
+        <v>Hunter Defense</v>
+      </c>
+      <c r="C163">
+        <v>2</v>
+      </c>
+      <c r="D163" t="str">
+        <v>+3.8%</v>
+      </c>
+      <c r="E163">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B164" t="str">
+        <v>Hunter Defense</v>
+      </c>
+      <c r="C164">
+        <v>3</v>
+      </c>
+      <c r="D164" t="str">
+        <v>+5.8%</v>
+      </c>
+      <c r="E164">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B165" t="str">
+        <v>Hunter Defense</v>
+      </c>
+      <c r="C165">
+        <v>4</v>
+      </c>
+      <c r="D165" t="str">
+        <v>+7.7%</v>
+      </c>
+      <c r="E165">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B166" t="str">
+        <v>Hunter Defense</v>
+      </c>
+      <c r="C166">
+        <v>5</v>
+      </c>
+      <c r="D166" t="str">
+        <v>+9.6%</v>
+      </c>
+      <c r="E166">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B167" t="str">
+        <v>Hunter Defense</v>
+      </c>
+      <c r="C167">
+        <v>6</v>
+      </c>
+      <c r="D167" t="str">
+        <v>+11.5%</v>
+      </c>
+      <c r="E167">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B168" t="str">
+        <v>Hunter Defense</v>
+      </c>
+      <c r="C168">
+        <v>7</v>
+      </c>
+      <c r="D168" t="str">
+        <v>+13.4%</v>
+      </c>
+      <c r="E168">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B169" t="str">
+        <v>Hunter Defense</v>
+      </c>
+      <c r="C169">
+        <v>8</v>
+      </c>
+      <c r="D169" t="str">
+        <v>+15.4%</v>
+      </c>
+      <c r="E169">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B170" t="str">
+        <v>Hunter Defense</v>
+      </c>
+      <c r="C170">
+        <v>9</v>
+      </c>
+      <c r="D170" t="str">
+        <v>+17.3%</v>
+      </c>
+      <c r="E170">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B171" t="str">
+        <v>Hunter Defense</v>
+      </c>
+      <c r="C171">
+        <v>10</v>
+      </c>
+      <c r="D171" t="str">
+        <v>+19.2%</v>
+      </c>
+      <c r="E171">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B172" t="str">
+        <v>Hunter Attack</v>
+      </c>
+      <c r="C172">
+        <v>1</v>
+      </c>
+      <c r="D172" t="str">
+        <v>+1.9%</v>
+      </c>
+      <c r="E172">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B173" t="str">
+        <v>Hunter Attack</v>
+      </c>
+      <c r="C173">
+        <v>2</v>
+      </c>
+      <c r="D173" t="str">
+        <v>+3.8%</v>
+      </c>
+      <c r="E173">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B174" t="str">
+        <v>Hunter Attack</v>
+      </c>
+      <c r="C174">
+        <v>3</v>
+      </c>
+      <c r="D174" t="str">
+        <v>+5.8%</v>
+      </c>
+      <c r="E174">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B175" t="str">
+        <v>Hunter Attack</v>
+      </c>
+      <c r="C175">
+        <v>4</v>
+      </c>
+      <c r="D175" t="str">
+        <v>+7.7%</v>
+      </c>
+      <c r="E175">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B176" t="str">
+        <v>Hunter Attack</v>
+      </c>
+      <c r="C176">
+        <v>5</v>
+      </c>
+      <c r="D176" t="str">
+        <v>+9.6%</v>
+      </c>
+      <c r="E176">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B177" t="str">
+        <v>Hunter Attack</v>
+      </c>
+      <c r="C177">
+        <v>6</v>
+      </c>
+      <c r="D177" t="str">
+        <v>+11.5%</v>
+      </c>
+      <c r="E177">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B178" t="str">
+        <v>Hunter Attack</v>
+      </c>
+      <c r="C178">
+        <v>7</v>
+      </c>
+      <c r="D178" t="str">
+        <v>+13.4%</v>
+      </c>
+      <c r="E178">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B179" t="str">
+        <v>Hunter Attack</v>
+      </c>
+      <c r="C179">
+        <v>8</v>
+      </c>
+      <c r="D179" t="str">
+        <v>+15.4%</v>
+      </c>
+      <c r="E179">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B180" t="str">
+        <v>Hunter Attack</v>
+      </c>
+      <c r="C180">
+        <v>9</v>
+      </c>
+      <c r="D180" t="str">
+        <v>+17.3%</v>
+      </c>
+      <c r="E180">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B181" t="str">
+        <v>Hunter Attack</v>
+      </c>
+      <c r="C181">
+        <v>10</v>
+      </c>
+      <c r="D181" t="str">
+        <v>+19.2%</v>
+      </c>
+      <c r="E181">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B182" t="str">
+        <v>Hunter Health</v>
+      </c>
+      <c r="C182">
+        <v>1</v>
+      </c>
+      <c r="D182" t="str">
+        <v>+1.4%</v>
+      </c>
+      <c r="E182">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B183" t="str">
+        <v>Hunter Health</v>
+      </c>
+      <c r="C183">
+        <v>2</v>
+      </c>
+      <c r="D183" t="str">
+        <v>+2.9%</v>
+      </c>
+      <c r="E183">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B184" t="str">
+        <v>Hunter Health</v>
+      </c>
+      <c r="C184">
+        <v>3</v>
+      </c>
+      <c r="D184" t="str">
+        <v>+4.3%</v>
+      </c>
+      <c r="E184">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B185" t="str">
+        <v>Hunter Health</v>
+      </c>
+      <c r="C185">
+        <v>4</v>
+      </c>
+      <c r="D185" t="str">
+        <v>+5.8%</v>
+      </c>
+      <c r="E185">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B186" t="str">
+        <v>Hunter Health</v>
+      </c>
+      <c r="C186">
+        <v>5</v>
+      </c>
+      <c r="D186" t="str">
+        <v>+7.2%</v>
+      </c>
+      <c r="E186">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B187" t="str">
+        <v>Hunter Health</v>
+      </c>
+      <c r="C187">
+        <v>6</v>
+      </c>
+      <c r="D187" t="str">
+        <v>+8.6%</v>
+      </c>
+      <c r="E187">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B188" t="str">
+        <v>Hunter Health</v>
+      </c>
+      <c r="C188">
+        <v>7</v>
+      </c>
+      <c r="D188" t="str">
+        <v>+10.1%</v>
+      </c>
+      <c r="E188">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B189" t="str">
+        <v>Hunter Health</v>
+      </c>
+      <c r="C189">
+        <v>8</v>
+      </c>
+      <c r="D189" t="str">
+        <v>+11.5%</v>
+      </c>
+      <c r="E189">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B190" t="str">
+        <v>Hunter Health</v>
+      </c>
+      <c r="C190">
+        <v>9</v>
+      </c>
+      <c r="D190" t="str">
+        <v>+13%</v>
+      </c>
+      <c r="E190">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B191" t="str">
+        <v>Hunter Health</v>
+      </c>
+      <c r="C191">
+        <v>10</v>
+      </c>
+      <c r="D191" t="str">
+        <v>+14.4%</v>
+      </c>
+      <c r="E191">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B192" t="str">
+        <v>Hunter Lethality</v>
+      </c>
+      <c r="C192">
+        <v>1</v>
+      </c>
+      <c r="D192" t="str">
+        <v>+1.4%</v>
+      </c>
+      <c r="E192">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B193" t="str">
+        <v>Hunter Lethality</v>
+      </c>
+      <c r="C193">
+        <v>2</v>
+      </c>
+      <c r="D193" t="str">
+        <v>+2.9%</v>
+      </c>
+      <c r="E193">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B194" t="str">
+        <v>Hunter Lethality</v>
+      </c>
+      <c r="C194">
+        <v>3</v>
+      </c>
+      <c r="D194" t="str">
+        <v>+4.3%</v>
+      </c>
+      <c r="E194">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B195" t="str">
+        <v>Hunter Lethality</v>
+      </c>
+      <c r="C195">
+        <v>4</v>
+      </c>
+      <c r="D195" t="str">
+        <v>+5.8%</v>
+      </c>
+      <c r="E195">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B196" t="str">
+        <v>Hunter Lethality</v>
+      </c>
+      <c r="C196">
+        <v>5</v>
+      </c>
+      <c r="D196" t="str">
+        <v>+7.2%</v>
+      </c>
+      <c r="E196">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B197" t="str">
+        <v>Hunter Lethality</v>
+      </c>
+      <c r="C197">
+        <v>6</v>
+      </c>
+      <c r="D197" t="str">
+        <v>+8.6%</v>
+      </c>
+      <c r="E197">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B198" t="str">
+        <v>Hunter Lethality</v>
+      </c>
+      <c r="C198">
+        <v>7</v>
+      </c>
+      <c r="D198" t="str">
+        <v>+10.1%</v>
+      </c>
+      <c r="E198">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B199" t="str">
+        <v>Hunter Lethality</v>
+      </c>
+      <c r="C199">
+        <v>8</v>
+      </c>
+      <c r="D199" t="str">
+        <v>+11.5%</v>
+      </c>
+      <c r="E199">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B200" t="str">
+        <v>Hunter Lethality</v>
+      </c>
+      <c r="C200">
+        <v>9</v>
+      </c>
+      <c r="D200" t="str">
+        <v>+13%</v>
+      </c>
+      <c r="E200">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B201" t="str">
+        <v>Hunter Lethality</v>
+      </c>
+      <c r="C201">
+        <v>10</v>
+      </c>
+      <c r="D201" t="str">
+        <v>+14.4%</v>
+      </c>
+      <c r="E201">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B202" t="str">
+        <v>Rider Attack</v>
+      </c>
+      <c r="C202">
+        <v>1</v>
+      </c>
+      <c r="D202" t="str">
+        <v>+1.9%</v>
+      </c>
+      <c r="E202">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B203" t="str">
+        <v>Rider Attack</v>
+      </c>
+      <c r="C203">
+        <v>2</v>
+      </c>
+      <c r="D203" t="str">
+        <v>+3.8%</v>
+      </c>
+      <c r="E203">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B204" t="str">
+        <v>Rider Attack</v>
+      </c>
+      <c r="C204">
+        <v>3</v>
+      </c>
+      <c r="D204" t="str">
+        <v>+5.8%</v>
+      </c>
+      <c r="E204">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B205" t="str">
+        <v>Rider Attack</v>
+      </c>
+      <c r="C205">
+        <v>4</v>
+      </c>
+      <c r="D205" t="str">
+        <v>+7.7%</v>
+      </c>
+      <c r="E205">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B206" t="str">
+        <v>Rider Attack</v>
+      </c>
+      <c r="C206">
+        <v>5</v>
+      </c>
+      <c r="D206" t="str">
+        <v>+9.6%</v>
+      </c>
+      <c r="E206">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B207" t="str">
+        <v>Rider Attack</v>
+      </c>
+      <c r="C207">
+        <v>6</v>
+      </c>
+      <c r="D207" t="str">
+        <v>+11.5%</v>
+      </c>
+      <c r="E207">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B208" t="str">
+        <v>Rider Attack</v>
+      </c>
+      <c r="C208">
+        <v>7</v>
+      </c>
+      <c r="D208" t="str">
+        <v>+13.4%</v>
+      </c>
+      <c r="E208">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B209" t="str">
+        <v>Rider Attack</v>
+      </c>
+      <c r="C209">
+        <v>8</v>
+      </c>
+      <c r="D209" t="str">
+        <v>+15.4%</v>
+      </c>
+      <c r="E209">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B210" t="str">
+        <v>Rider Attack</v>
+      </c>
+      <c r="C210">
+        <v>9</v>
+      </c>
+      <c r="D210" t="str">
+        <v>+17.3%</v>
+      </c>
+      <c r="E210">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B211" t="str">
+        <v>Rider Attack</v>
+      </c>
+      <c r="C211">
+        <v>10</v>
+      </c>
+      <c r="D211" t="str">
+        <v>+19.2%</v>
+      </c>
+      <c r="E211">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B212" t="str">
+        <v>Rider Health</v>
+      </c>
+      <c r="C212">
+        <v>1</v>
+      </c>
+      <c r="D212" t="str">
+        <v>+1.4%</v>
+      </c>
+      <c r="E212">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B213" t="str">
+        <v>Rider Health</v>
+      </c>
+      <c r="C213">
+        <v>2</v>
+      </c>
+      <c r="D213" t="str">
+        <v>+2.9%</v>
+      </c>
+      <c r="E213">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B214" t="str">
+        <v>Rider Health</v>
+      </c>
+      <c r="C214">
+        <v>3</v>
+      </c>
+      <c r="D214" t="str">
+        <v>+4.3%</v>
+      </c>
+      <c r="E214">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B215" t="str">
+        <v>Rider Health</v>
+      </c>
+      <c r="C215">
+        <v>4</v>
+      </c>
+      <c r="D215" t="str">
+        <v>+5.8%</v>
+      </c>
+      <c r="E215">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B216" t="str">
+        <v>Rider Health</v>
+      </c>
+      <c r="C216">
+        <v>5</v>
+      </c>
+      <c r="D216" t="str">
+        <v>+7.2%</v>
+      </c>
+      <c r="E216">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B217" t="str">
+        <v>Rider Health</v>
+      </c>
+      <c r="C217">
+        <v>6</v>
+      </c>
+      <c r="D217" t="str">
+        <v>+8.6%</v>
+      </c>
+      <c r="E217">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B218" t="str">
+        <v>Rider Health</v>
+      </c>
+      <c r="C218">
+        <v>7</v>
+      </c>
+      <c r="D218" t="str">
+        <v>+10.1%</v>
+      </c>
+      <c r="E218">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B219" t="str">
+        <v>Rider Health</v>
+      </c>
+      <c r="C219">
+        <v>8</v>
+      </c>
+      <c r="D219" t="str">
+        <v>+11.5%</v>
+      </c>
+      <c r="E219">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B220" t="str">
+        <v>Rider Health</v>
+      </c>
+      <c r="C220">
+        <v>9</v>
+      </c>
+      <c r="D220" t="str">
+        <v>+13%</v>
+      </c>
+      <c r="E220">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B221" t="str">
+        <v>Rider Health</v>
+      </c>
+      <c r="C221">
+        <v>10</v>
+      </c>
+      <c r="D221" t="str">
+        <v>+14.4%</v>
+      </c>
+      <c r="E221">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B222" t="str">
+        <v>Rider Lethality</v>
+      </c>
+      <c r="C222">
+        <v>1</v>
+      </c>
+      <c r="D222" t="str">
+        <v>+1.4%</v>
+      </c>
+      <c r="E222">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B223" t="str">
+        <v>Rider Lethality</v>
+      </c>
+      <c r="C223">
+        <v>2</v>
+      </c>
+      <c r="D223" t="str">
+        <v>+2.9%</v>
+      </c>
+      <c r="E223">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B224" t="str">
+        <v>Rider Lethality</v>
+      </c>
+      <c r="C224">
+        <v>3</v>
+      </c>
+      <c r="D224" t="str">
+        <v>+4.3%</v>
+      </c>
+      <c r="E224">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B225" t="str">
+        <v>Rider Lethality</v>
+      </c>
+      <c r="C225">
+        <v>4</v>
+      </c>
+      <c r="D225" t="str">
+        <v>+5.8%</v>
+      </c>
+      <c r="E225">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B226" t="str">
+        <v>Rider Lethality</v>
+      </c>
+      <c r="C226">
+        <v>5</v>
+      </c>
+      <c r="D226" t="str">
+        <v>+7.2%</v>
+      </c>
+      <c r="E226">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B227" t="str">
+        <v>Rider Lethality</v>
+      </c>
+      <c r="C227">
+        <v>6</v>
+      </c>
+      <c r="D227" t="str">
+        <v>+8.6%</v>
+      </c>
+      <c r="E227">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B228" t="str">
+        <v>Rider Lethality</v>
+      </c>
+      <c r="C228">
+        <v>7</v>
+      </c>
+      <c r="D228" t="str">
+        <v>+10.1%</v>
+      </c>
+      <c r="E228">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B229" t="str">
+        <v>Rider Lethality</v>
+      </c>
+      <c r="C229">
+        <v>8</v>
+      </c>
+      <c r="D229" t="str">
+        <v>+11.5%</v>
+      </c>
+      <c r="E229">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B230" t="str">
+        <v>Rider Lethality</v>
+      </c>
+      <c r="C230">
+        <v>9</v>
+      </c>
+      <c r="D230" t="str">
+        <v>+13%</v>
+      </c>
+      <c r="E230">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="str">
+        <v>Infantry Attack</v>
+      </c>
+      <c r="B231" t="str">
+        <v>Rider Lethality</v>
+      </c>
+      <c r="C231">
+        <v>10</v>
+      </c>
+      <c r="D231" t="str">
+        <v>+14.4%</v>
+      </c>
+      <c r="E231">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B232" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="C232">
+        <v>1</v>
+      </c>
+      <c r="D232" t="str">
+        <v>Every 10 turns, fires a missile that deals 70% damage to the enemy front row.</v>
+      </c>
+      <c r="E232">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B233" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="C233">
+        <v>2</v>
+      </c>
+      <c r="D233" t="str">
+        <v>Every 10 turns, fires a missile that deals 90% damage to the enemy front row.</v>
+      </c>
+      <c r="E233">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B234" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="C234">
+        <v>3</v>
+      </c>
+      <c r="D234" t="str">
+        <v>Every 10 turns, fires a missile that deals 115% damage to the enemy front row.</v>
+      </c>
+      <c r="E234">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B235" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="C235">
+        <v>4</v>
+      </c>
+      <c r="D235" t="str">
+        <v>Attack interval is reduced to 9.</v>
+      </c>
+      <c r="E235">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B236" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="C236">
+        <v>5</v>
+      </c>
+      <c r="D236" t="str">
+        <v>Every 9 turns, fires a missile that deals 135% damage to the enemy front row.</v>
+      </c>
+      <c r="E236">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B237" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="C237">
+        <v>6</v>
+      </c>
+      <c r="D237" t="str">
+        <v>The skill now targets all enemies.</v>
+      </c>
+      <c r="E237">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B238" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="C238">
+        <v>7</v>
+      </c>
+      <c r="D238" t="str">
+        <v>Every 9 turns, fires a missile that deals 160% damage to the enemy front row.</v>
+      </c>
+      <c r="E238">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B239" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="C239">
+        <v>8</v>
+      </c>
+      <c r="D239" t="str">
+        <v>Attack interval is reduced to 8.</v>
+      </c>
+      <c r="E239">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B240" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="C240">
+        <v>9</v>
+      </c>
+      <c r="D240" t="str">
+        <v>Every 8 turns, fires a missile that deals 180% damage to the enemy front row.</v>
+      </c>
+      <c r="E240">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B241" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="C241">
+        <v>10</v>
+      </c>
+      <c r="D241" t="str">
+        <v>The skill is now triggered at the start of battle.</v>
+      </c>
+      <c r="E241">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B242" t="str">
+        <v>Troop Attack</v>
+      </c>
+      <c r="C242">
+        <v>1</v>
+      </c>
+      <c r="D242" t="str">
+        <v>+0.6%</v>
+      </c>
+      <c r="E242">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B243" t="str">
+        <v>Troop Attack</v>
+      </c>
+      <c r="C243">
+        <v>2</v>
+      </c>
+      <c r="D243" t="str">
+        <v>+1.3%</v>
+      </c>
+      <c r="E243">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B244" t="str">
+        <v>Troop Attack</v>
+      </c>
+      <c r="C244">
+        <v>3</v>
+      </c>
+      <c r="D244" t="str">
+        <v>+1.9%</v>
+      </c>
+      <c r="E244">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B245" t="str">
+        <v>Troop Attack</v>
+      </c>
+      <c r="C245">
+        <v>4</v>
+      </c>
+      <c r="D245" t="str">
+        <v>+2.6%</v>
+      </c>
+      <c r="E245">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B246" t="str">
+        <v>Troop Attack</v>
+      </c>
+      <c r="C246">
+        <v>5</v>
+      </c>
+      <c r="D246" t="str">
+        <v>+3.2%</v>
+      </c>
+      <c r="E246">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B247" t="str">
+        <v>Troop Attack</v>
+      </c>
+      <c r="C247">
+        <v>6</v>
+      </c>
+      <c r="D247" t="str">
+        <v>+3.8%</v>
+      </c>
+      <c r="E247">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B248" t="str">
+        <v>Troop Attack</v>
+      </c>
+      <c r="C248">
+        <v>7</v>
+      </c>
+      <c r="D248" t="str">
+        <v>+4.5%</v>
+      </c>
+      <c r="E248">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B249" t="str">
+        <v>Troop Attack</v>
+      </c>
+      <c r="C249">
+        <v>8</v>
+      </c>
+      <c r="D249" t="str">
+        <v>+5.1%</v>
+      </c>
+      <c r="E249">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B250" t="str">
+        <v>Troop Attack</v>
+      </c>
+      <c r="C250">
+        <v>9</v>
+      </c>
+      <c r="D250" t="str">
+        <v>+5.8%</v>
+      </c>
+      <c r="E250">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B251" t="str">
+        <v>Troop Attack</v>
+      </c>
+      <c r="C251">
+        <v>10</v>
+      </c>
+      <c r="D251" t="str">
+        <v>+6.4%</v>
+      </c>
+      <c r="E251">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B252" t="str">
+        <v>Troop Defense</v>
+      </c>
+      <c r="C252">
+        <v>1</v>
+      </c>
+      <c r="D252" t="str">
+        <v>+0.6%</v>
+      </c>
+      <c r="E252">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B253" t="str">
+        <v>Troop Defense</v>
+      </c>
+      <c r="C253">
+        <v>2</v>
+      </c>
+      <c r="D253" t="str">
+        <v>+1.3%</v>
+      </c>
+      <c r="E253">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B254" t="str">
+        <v>Troop Defense</v>
+      </c>
+      <c r="C254">
+        <v>3</v>
+      </c>
+      <c r="D254" t="str">
+        <v>+1.9%</v>
+      </c>
+      <c r="E254">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B255" t="str">
+        <v>Troop Defense</v>
+      </c>
+      <c r="C255">
+        <v>4</v>
+      </c>
+      <c r="D255" t="str">
+        <v>+2.6%</v>
+      </c>
+      <c r="E255">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B256" t="str">
+        <v>Troop Defense</v>
+      </c>
+      <c r="C256">
+        <v>5</v>
+      </c>
+      <c r="D256" t="str">
+        <v>+3.2%</v>
+      </c>
+      <c r="E256">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B257" t="str">
+        <v>Troop Defense</v>
+      </c>
+      <c r="C257">
+        <v>6</v>
+      </c>
+      <c r="D257" t="str">
+        <v>+3.8%</v>
+      </c>
+      <c r="E257">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B258" t="str">
+        <v>Troop Defense</v>
+      </c>
+      <c r="C258">
+        <v>7</v>
+      </c>
+      <c r="D258" t="str">
+        <v>+4.5%</v>
+      </c>
+      <c r="E258">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B259" t="str">
+        <v>Troop Defense</v>
+      </c>
+      <c r="C259">
+        <v>8</v>
+      </c>
+      <c r="D259" t="str">
+        <v>+5.1%</v>
+      </c>
+      <c r="E259">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B260" t="str">
+        <v>Troop Defense</v>
+      </c>
+      <c r="C260">
+        <v>9</v>
+      </c>
+      <c r="D260" t="str">
+        <v>+5.8%</v>
+      </c>
+      <c r="E260">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B261" t="str">
+        <v>Troop Defense</v>
+      </c>
+      <c r="C261">
+        <v>10</v>
+      </c>
+      <c r="D261" t="str">
+        <v>+6.4%</v>
+      </c>
+      <c r="E261">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B262" t="str">
+        <v>Troop Lethality</v>
+      </c>
+      <c r="C262">
+        <v>1</v>
+      </c>
+      <c r="D262" t="str">
+        <v>+0.5%</v>
+      </c>
+      <c r="E262">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B263" t="str">
+        <v>Troop Lethality</v>
+      </c>
+      <c r="C263">
+        <v>2</v>
+      </c>
+      <c r="D263" t="str">
+        <v>+1%</v>
+      </c>
+      <c r="E263">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B264" t="str">
+        <v>Troop Lethality</v>
+      </c>
+      <c r="C264">
+        <v>3</v>
+      </c>
+      <c r="D264" t="str">
+        <v>+1.4%</v>
+      </c>
+      <c r="E264">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B265" t="str">
+        <v>Troop Lethality</v>
+      </c>
+      <c r="C265">
+        <v>4</v>
+      </c>
+      <c r="D265" t="str">
+        <v>+1.9%</v>
+      </c>
+      <c r="E265">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B266" t="str">
+        <v>Troop Lethality</v>
+      </c>
+      <c r="C266">
+        <v>5</v>
+      </c>
+      <c r="D266" t="str">
+        <v>+2.4%</v>
+      </c>
+      <c r="E266">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B267" t="str">
+        <v>Troop Lethality</v>
+      </c>
+      <c r="C267">
+        <v>6</v>
+      </c>
+      <c r="D267" t="str">
+        <v>+2.9%</v>
+      </c>
+      <c r="E267">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B268" t="str">
+        <v>Troop Lethality</v>
+      </c>
+      <c r="C268">
+        <v>7</v>
+      </c>
+      <c r="D268" t="str">
+        <v>+3.4%</v>
+      </c>
+      <c r="E268">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B269" t="str">
+        <v>Troop Lethality</v>
+      </c>
+      <c r="C269">
+        <v>8</v>
+      </c>
+      <c r="D269" t="str">
+        <v>+3.8%</v>
+      </c>
+      <c r="E269">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B270" t="str">
+        <v>Troop Lethality</v>
+      </c>
+      <c r="C270">
+        <v>9</v>
+      </c>
+      <c r="D270" t="str">
+        <v>+4.3%</v>
+      </c>
+      <c r="E270">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B271" t="str">
+        <v>Troop Lethality</v>
+      </c>
+      <c r="C271">
+        <v>10</v>
+      </c>
+      <c r="D271" t="str">
+        <v>+4.8%</v>
+      </c>
+      <c r="E271">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B272" t="str">
+        <v>Troop Health</v>
+      </c>
+      <c r="C272">
+        <v>1</v>
+      </c>
+      <c r="D272" t="str">
+        <v>+0.5%</v>
+      </c>
+      <c r="E272">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B273" t="str">
+        <v>Troop Health</v>
+      </c>
+      <c r="C273">
+        <v>2</v>
+      </c>
+      <c r="D273" t="str">
+        <v>+1%</v>
+      </c>
+      <c r="E273">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B274" t="str">
+        <v>Troop Health</v>
+      </c>
+      <c r="C274">
+        <v>3</v>
+      </c>
+      <c r="D274" t="str">
+        <v>+1.4%</v>
+      </c>
+      <c r="E274">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B275" t="str">
+        <v>Troop Health</v>
+      </c>
+      <c r="C275">
+        <v>4</v>
+      </c>
+      <c r="D275" t="str">
+        <v>+1.9%</v>
+      </c>
+      <c r="E275">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B276" t="str">
+        <v>Troop Health</v>
+      </c>
+      <c r="C276">
+        <v>5</v>
+      </c>
+      <c r="D276" t="str">
+        <v>+2.4%</v>
+      </c>
+      <c r="E276">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B277" t="str">
+        <v>Troop Health</v>
+      </c>
+      <c r="C277">
+        <v>6</v>
+      </c>
+      <c r="D277" t="str">
+        <v>+2.9%</v>
+      </c>
+      <c r="E277">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B278" t="str">
+        <v>Troop Health</v>
+      </c>
+      <c r="C278">
+        <v>7</v>
+      </c>
+      <c r="D278" t="str">
+        <v>+3.4%</v>
+      </c>
+      <c r="E278">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B279" t="str">
+        <v>Troop Health</v>
+      </c>
+      <c r="C279">
+        <v>8</v>
+      </c>
+      <c r="D279" t="str">
+        <v>+3.8%</v>
+      </c>
+      <c r="E279">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B280" t="str">
+        <v>Troop Health</v>
+      </c>
+      <c r="C280">
+        <v>9</v>
+      </c>
+      <c r="D280" t="str">
+        <v>+4.3%</v>
+      </c>
+      <c r="E280">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B281" t="str">
+        <v>Troop Health</v>
+      </c>
+      <c r="C281">
+        <v>10</v>
+      </c>
+      <c r="D281" t="str">
+        <v>+4.8%</v>
+      </c>
+      <c r="E281">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B282" t="str">
+        <v>March Capacity</v>
+      </c>
+      <c r="C282">
+        <v>1</v>
+      </c>
+      <c r="D282" t="str">
+        <v>+70</v>
+      </c>
+      <c r="E282">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B283" t="str">
+        <v>March Capacity</v>
+      </c>
+      <c r="C283">
+        <v>2</v>
+      </c>
+      <c r="D283" t="str">
+        <v>+140</v>
+      </c>
+      <c r="E283">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B284" t="str">
+        <v>March Capacity</v>
+      </c>
+      <c r="C284">
+        <v>3</v>
+      </c>
+      <c r="D284" t="str">
+        <v>+210</v>
+      </c>
+      <c r="E284">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B285" t="str">
+        <v>March Capacity</v>
+      </c>
+      <c r="C285">
+        <v>4</v>
+      </c>
+      <c r="D285" t="str">
+        <v>+280</v>
+      </c>
+      <c r="E285">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B286" t="str">
+        <v>March Capacity</v>
+      </c>
+      <c r="C286">
+        <v>5</v>
+      </c>
+      <c r="D286" t="str">
+        <v>+350</v>
+      </c>
+      <c r="E286">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B287" t="str">
+        <v>March Capacity</v>
+      </c>
+      <c r="C287">
+        <v>6</v>
+      </c>
+      <c r="D287" t="str">
+        <v>+420</v>
+      </c>
+      <c r="E287">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B288" t="str">
+        <v>March Capacity</v>
+      </c>
+      <c r="C288">
+        <v>7</v>
+      </c>
+      <c r="D288" t="str">
+        <v>+490</v>
+      </c>
+      <c r="E288">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B289" t="str">
+        <v>March Capacity</v>
+      </c>
+      <c r="C289">
+        <v>8</v>
+      </c>
+      <c r="D289" t="str">
+        <v>+560</v>
+      </c>
+      <c r="E289">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B290" t="str">
+        <v>March Capacity</v>
+      </c>
+      <c r="C290">
+        <v>9</v>
+      </c>
+      <c r="D290" t="str">
+        <v>+630</v>
+      </c>
+      <c r="E290">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B291" t="str">
+        <v>March Capacity</v>
+      </c>
+      <c r="C291">
+        <v>10</v>
+      </c>
+      <c r="D291" t="str">
+        <v>+700</v>
+      </c>
+      <c r="E291">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B292" t="str">
+        <v>Rally Attack</v>
+      </c>
+      <c r="C292">
+        <v>1</v>
+      </c>
+      <c r="D292" t="str">
+        <v>+0.6%</v>
+      </c>
+      <c r="E292">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B293" t="str">
+        <v>Rally Attack</v>
+      </c>
+      <c r="C293">
+        <v>2</v>
+      </c>
+      <c r="D293" t="str">
+        <v>+1.3%</v>
+      </c>
+      <c r="E293">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B294" t="str">
+        <v>Rally Attack</v>
+      </c>
+      <c r="C294">
+        <v>3</v>
+      </c>
+      <c r="D294" t="str">
+        <v>+1.9%</v>
+      </c>
+      <c r="E294">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B295" t="str">
+        <v>Rally Attack</v>
+      </c>
+      <c r="C295">
+        <v>4</v>
+      </c>
+      <c r="D295" t="str">
+        <v>+2.6%</v>
+      </c>
+      <c r="E295">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B296" t="str">
+        <v>Rally Attack</v>
+      </c>
+      <c r="C296">
+        <v>5</v>
+      </c>
+      <c r="D296" t="str">
+        <v>+3.2%</v>
+      </c>
+      <c r="E296">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B297" t="str">
+        <v>Rally Attack</v>
+      </c>
+      <c r="C297">
+        <v>6</v>
+      </c>
+      <c r="D297" t="str">
+        <v>+3.8%</v>
+      </c>
+      <c r="E297">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B298" t="str">
+        <v>Rally Attack</v>
+      </c>
+      <c r="C298">
+        <v>7</v>
+      </c>
+      <c r="D298" t="str">
+        <v>+4.5%</v>
+      </c>
+      <c r="E298">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B299" t="str">
+        <v>Rally Attack</v>
+      </c>
+      <c r="C299">
+        <v>8</v>
+      </c>
+      <c r="D299" t="str">
+        <v>+5.1%</v>
+      </c>
+      <c r="E299">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B300" t="str">
+        <v>Rally Attack</v>
+      </c>
+      <c r="C300">
+        <v>9</v>
+      </c>
+      <c r="D300" t="str">
+        <v>+5.8%</v>
+      </c>
+      <c r="E300">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B301" t="str">
+        <v>Rally Attack</v>
+      </c>
+      <c r="C301">
+        <v>10</v>
+      </c>
+      <c r="D301" t="str">
+        <v>+6.4%</v>
+      </c>
+      <c r="E301">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B302" t="str">
+        <v>Rally Defense</v>
+      </c>
+      <c r="C302">
+        <v>1</v>
+      </c>
+      <c r="D302" t="str">
+        <v>+0.6%</v>
+      </c>
+      <c r="E302">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B303" t="str">
+        <v>Rally Defense</v>
+      </c>
+      <c r="C303">
+        <v>2</v>
+      </c>
+      <c r="D303" t="str">
+        <v>+1.3%</v>
+      </c>
+      <c r="E303">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B304" t="str">
+        <v>Rally Defense</v>
+      </c>
+      <c r="C304">
+        <v>3</v>
+      </c>
+      <c r="D304" t="str">
+        <v>+1.9%</v>
+      </c>
+      <c r="E304">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B305" t="str">
+        <v>Rally Defense</v>
+      </c>
+      <c r="C305">
+        <v>4</v>
+      </c>
+      <c r="D305" t="str">
+        <v>+2.6%</v>
+      </c>
+      <c r="E305">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B306" t="str">
+        <v>Rally Defense</v>
+      </c>
+      <c r="C306">
+        <v>5</v>
+      </c>
+      <c r="D306" t="str">
+        <v>+3.2%</v>
+      </c>
+      <c r="E306">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B307" t="str">
+        <v>Rally Defense</v>
+      </c>
+      <c r="C307">
+        <v>6</v>
+      </c>
+      <c r="D307" t="str">
+        <v>+3.8%</v>
+      </c>
+      <c r="E307">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B308" t="str">
+        <v>Rally Defense</v>
+      </c>
+      <c r="C308">
+        <v>7</v>
+      </c>
+      <c r="D308" t="str">
+        <v>+4.5%</v>
+      </c>
+      <c r="E308">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B309" t="str">
+        <v>Rally Defense</v>
+      </c>
+      <c r="C309">
+        <v>8</v>
+      </c>
+      <c r="D309" t="str">
+        <v>+5.1%</v>
+      </c>
+      <c r="E309">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B310" t="str">
+        <v>Rally Defense</v>
+      </c>
+      <c r="C310">
+        <v>9</v>
+      </c>
+      <c r="D310" t="str">
+        <v>+5.8%</v>
+      </c>
+      <c r="E310">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B311" t="str">
+        <v>Rally Defense</v>
+      </c>
+      <c r="C311">
+        <v>10</v>
+      </c>
+      <c r="D311" t="str">
+        <v>+6.4%</v>
+      </c>
+      <c r="E311">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B312" t="str">
+        <v>Rally Lethality</v>
+      </c>
+      <c r="C312">
+        <v>1</v>
+      </c>
+      <c r="D312" t="str">
+        <v>+0.5%</v>
+      </c>
+      <c r="E312">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B313" t="str">
+        <v>Rally Lethality</v>
+      </c>
+      <c r="C313">
+        <v>2</v>
+      </c>
+      <c r="D313" t="str">
+        <v>+1%</v>
+      </c>
+      <c r="E313">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B314" t="str">
+        <v>Rally Lethality</v>
+      </c>
+      <c r="C314">
+        <v>3</v>
+      </c>
+      <c r="D314" t="str">
+        <v>+1.4%</v>
+      </c>
+      <c r="E314">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B315" t="str">
+        <v>Rally Lethality</v>
+      </c>
+      <c r="C315">
+        <v>4</v>
+      </c>
+      <c r="D315" t="str">
+        <v>+1.9%</v>
+      </c>
+      <c r="E315">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B316" t="str">
+        <v>Rally Lethality</v>
+      </c>
+      <c r="C316">
+        <v>5</v>
+      </c>
+      <c r="D316" t="str">
+        <v>+2.4%</v>
+      </c>
+      <c r="E316">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B317" t="str">
+        <v>Rally Lethality</v>
+      </c>
+      <c r="C317">
+        <v>6</v>
+      </c>
+      <c r="D317" t="str">
+        <v>+2.9%</v>
+      </c>
+      <c r="E317">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B318" t="str">
+        <v>Rally Lethality</v>
+      </c>
+      <c r="C318">
+        <v>7</v>
+      </c>
+      <c r="D318" t="str">
+        <v>+3.4%</v>
+      </c>
+      <c r="E318">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B319" t="str">
+        <v>Rally Lethality</v>
+      </c>
+      <c r="C319">
+        <v>8</v>
+      </c>
+      <c r="D319" t="str">
+        <v>+3.8%</v>
+      </c>
+      <c r="E319">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B320" t="str">
+        <v>Rally Lethality</v>
+      </c>
+      <c r="C320">
+        <v>9</v>
+      </c>
+      <c r="D320" t="str">
+        <v>+4.3%</v>
+      </c>
+      <c r="E320">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B321" t="str">
+        <v>Rally Lethality</v>
+      </c>
+      <c r="C321">
+        <v>10</v>
+      </c>
+      <c r="D321" t="str">
+        <v>+4.8%</v>
+      </c>
+      <c r="E321">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B322" t="str">
+        <v>Rally Health</v>
+      </c>
+      <c r="C322">
+        <v>1</v>
+      </c>
+      <c r="D322" t="str">
+        <v>+0.5%</v>
+      </c>
+      <c r="E322">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B323" t="str">
+        <v>Rally Health</v>
+      </c>
+      <c r="C323">
+        <v>2</v>
+      </c>
+      <c r="D323" t="str">
+        <v>+1%</v>
+      </c>
+      <c r="E323">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B324" t="str">
+        <v>Rally Health</v>
+      </c>
+      <c r="C324">
+        <v>3</v>
+      </c>
+      <c r="D324" t="str">
+        <v>+1.4%</v>
+      </c>
+      <c r="E324">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B325" t="str">
+        <v>Rally Health</v>
+      </c>
+      <c r="C325">
+        <v>4</v>
+      </c>
+      <c r="D325" t="str">
+        <v>+1.9%</v>
+      </c>
+      <c r="E325">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B326" t="str">
+        <v>Rally Health</v>
+      </c>
+      <c r="C326">
+        <v>5</v>
+      </c>
+      <c r="D326" t="str">
+        <v>+2.4%</v>
+      </c>
+      <c r="E326">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B327" t="str">
+        <v>Rally Health</v>
+      </c>
+      <c r="C327">
+        <v>6</v>
+      </c>
+      <c r="D327" t="str">
+        <v>+2.9%</v>
+      </c>
+      <c r="E327">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B328" t="str">
+        <v>Rally Health</v>
+      </c>
+      <c r="C328">
+        <v>7</v>
+      </c>
+      <c r="D328" t="str">
+        <v>+3.4%</v>
+      </c>
+      <c r="E328">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B329" t="str">
+        <v>Rally Health</v>
+      </c>
+      <c r="C329">
+        <v>8</v>
+      </c>
+      <c r="D329" t="str">
+        <v>+3.8%</v>
+      </c>
+      <c r="E329">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B330" t="str">
+        <v>Rally Health</v>
+      </c>
+      <c r="C330">
+        <v>9</v>
+      </c>
+      <c r="D330" t="str">
+        <v>+4.3%</v>
+      </c>
+      <c r="E330">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B331" t="str">
+        <v>Rally Health</v>
+      </c>
+      <c r="C331">
+        <v>10</v>
+      </c>
+      <c r="D331" t="str">
+        <v>+4.8%</v>
+      </c>
+      <c r="E331">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B332" t="str">
+        <v>Rally Capacity</v>
+      </c>
+      <c r="C332">
+        <v>1</v>
+      </c>
+      <c r="D332" t="str">
+        <v>+550</v>
+      </c>
+      <c r="E332">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B333" t="str">
+        <v>Rally Capacity</v>
+      </c>
+      <c r="C333">
+        <v>2</v>
+      </c>
+      <c r="D333" t="str">
+        <v>+1.1K</v>
+      </c>
+      <c r="E333">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B334" t="str">
+        <v>Rally Capacity</v>
+      </c>
+      <c r="C334">
+        <v>3</v>
+      </c>
+      <c r="D334" t="str">
+        <v>+1.65K</v>
+      </c>
+      <c r="E334">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B335" t="str">
+        <v>Rally Capacity</v>
+      </c>
+      <c r="C335">
+        <v>4</v>
+      </c>
+      <c r="D335" t="str">
+        <v>+2.2K</v>
+      </c>
+      <c r="E335">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B336" t="str">
+        <v>Rally Capacity</v>
+      </c>
+      <c r="C336">
+        <v>5</v>
+      </c>
+      <c r="D336" t="str">
+        <v>+2.75K</v>
+      </c>
+      <c r="E336">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B337" t="str">
+        <v>Rally Capacity</v>
+      </c>
+      <c r="C337">
+        <v>6</v>
+      </c>
+      <c r="D337" t="str">
+        <v>+3.3K</v>
+      </c>
+      <c r="E337">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B338" t="str">
+        <v>Rally Capacity</v>
+      </c>
+      <c r="C338">
+        <v>7</v>
+      </c>
+      <c r="D338" t="str">
+        <v>+3.85K</v>
+      </c>
+      <c r="E338">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B339" t="str">
+        <v>Rally Capacity</v>
+      </c>
+      <c r="C339">
+        <v>8</v>
+      </c>
+      <c r="D339" t="str">
+        <v>+4.4K</v>
+      </c>
+      <c r="E339">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B340" t="str">
+        <v>Rally Capacity</v>
+      </c>
+      <c r="C340">
+        <v>9</v>
+      </c>
+      <c r="D340" t="str">
+        <v>+4.95K</v>
+      </c>
+      <c r="E340">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B341" t="str">
+        <v>Rally Capacity</v>
+      </c>
+      <c r="C341">
+        <v>10</v>
+      </c>
+      <c r="D341" t="str">
+        <v>+5.5K</v>
+      </c>
+      <c r="E341">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B342" t="str">
+        <v>Adapt &amp;amp; Overcome</v>
+      </c>
+      <c r="C342">
+        <v>1</v>
+      </c>
+      <c r="D342" t="str">
+        <v>At the start of battle, applies a 550% shield to friendly Infantry.</v>
+      </c>
+      <c r="E342">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B343" t="str">
+        <v>Adapt &amp;amp; Overcome</v>
+      </c>
+      <c r="C343">
+        <v>2</v>
+      </c>
+      <c r="D343" t="str">
+        <v>At the start of battle, applies a 750% shield to friendly Infantry.</v>
+      </c>
+      <c r="E343">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B344" t="str">
+        <v>Adapt &amp;amp; Overcome</v>
+      </c>
+      <c r="C344">
+        <v>3</v>
+      </c>
+      <c r="D344" t="str">
+        <v>At the start of battle, applies a 1,000% shield to friendly Infantry.</v>
+      </c>
+      <c r="E344">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B345" t="str">
+        <v>Adapt &amp;amp; Overcome</v>
+      </c>
+      <c r="C345">
+        <v>4</v>
+      </c>
+      <c r="D345" t="str">
+        <v>Shield protection is extended to include Riders.</v>
+      </c>
+      <c r="E345">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B346" t="str">
+        <v>Adapt &amp;amp; Overcome</v>
+      </c>
+      <c r="C346">
+        <v>5</v>
+      </c>
+      <c r="D346" t="str">
+        <v>At the start of battle, applies a 1,200% shield to friendly Infantry and Riders.</v>
+      </c>
+      <c r="E346">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B347" t="str">
+        <v>Adapt &amp;amp; Overcome</v>
+      </c>
+      <c r="C347">
+        <v>6</v>
+      </c>
+      <c r="D347" t="str">
+        <v>An additional 150% shield is applied on turn 11.</v>
+      </c>
+      <c r="E347">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B348" t="str">
+        <v>Adapt &amp;amp; Overcome</v>
+      </c>
+      <c r="C348">
+        <v>7</v>
+      </c>
+      <c r="D348" t="str">
+        <v>On turns 1 and 11 applies a 1,200% and 450% shield respectively to Infantry and Riders.</v>
+      </c>
+      <c r="E348">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B349" t="str">
+        <v>Adapt &amp;amp; Overcome</v>
+      </c>
+      <c r="C349">
+        <v>8</v>
+      </c>
+      <c r="D349" t="str">
+        <v>Shield protection is extended to include all allies.</v>
+      </c>
+      <c r="E349">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B350" t="str">
+        <v>Adapt &amp;amp; Overcome</v>
+      </c>
+      <c r="C350">
+        <v>9</v>
+      </c>
+      <c r="D350" t="str">
+        <v>On turns 1 and 11 applies a 1,200% and 750% shield respectively to all allies.</v>
+      </c>
+      <c r="E350">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="str">
+        <v>Active Strike</v>
+      </c>
+      <c r="B351" t="str">
+        <v>Adapt &amp;amp; Overcome</v>
+      </c>
+      <c r="C351">
+        <v>10</v>
+      </c>
+      <c r="D351" t="str">
+        <v>On turns 1, 11, and 21, applies a 1,200%, 750%, and 300% shield respectively to all allies.</v>
+      </c>
+      <c r="E351">
+        <v>71</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E351"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E821"/>
   <sheetData>
     <row r="1">
@@ -14364,7 +20346,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E1201"/>
   <sheetData>
@@ -34790,4 +40772,190 @@
     <ignoredError numberStoredAsText="1" sqref="A1:E1201"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E3"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tree</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Skill</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Level</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Benefit</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Neuronal Medium</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Tree 1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Skill 1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Placeholder benefit</v>
+      </c>
+      <c r="E2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Tree 1</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Skill 2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Placeholder benefit</v>
+      </c>
+      <c r="E3">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E3"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tree</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Skill</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Level</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Benefit</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Neuronal Medium</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Tree 1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Skill 1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Placeholder benefit</v>
+      </c>
+      <c r="E2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Tree 1</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Skill 2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Placeholder benefit</v>
+      </c>
+      <c r="E3">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E3"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tree</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Skill</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Level</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Benefit</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Neuronal Medium</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Tree 1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Skill 1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Placeholder benefit</v>
+      </c>
+      <c r="E2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Tree 1</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Skill 2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Placeholder benefit</v>
+      </c>
+      <c r="E3">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
+  </ignoredErrors>
+</worksheet>
 </file>